--- a/12616274.xlsx
+++ b/12616274.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandeep kumar\Desktop\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E68AFD-8D8F-4F14-93CA-C850B4C11FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23309ED9-CF40-43BA-AF1C-02F149AD732D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,30 @@
   </si>
   <si>
     <t>Successfully understood complex concepts.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Strengthened subject knowledge through self-study.</t>
+  </si>
+  <si>
+    <t>Displayed dedication and commitment to studies.</t>
+  </si>
+  <si>
+    <t>Actively participated in classroom discussions.</t>
+  </si>
+  <si>
+    <t>Took initiative in learning new topics independently.</t>
+  </si>
+  <si>
+    <t>Remained focused on academic improvement.</t>
+  </si>
+  <si>
+    <t>Enhanced problem-solving and analytical skills.</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1390,7 @@
         <v>60</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" ref="I11:I22" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <f t="shared" ref="I11:I28" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>740</v>
       </c>
       <c r="J11" s="12">
@@ -1627,7 +1651,7 @@
         <v>40</v>
       </c>
       <c r="D17" s="11">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="E17" s="11">
         <v>120</v>
@@ -1643,11 +1667,11 @@
       </c>
       <c r="I17" s="12">
         <f t="shared" si="2"/>
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="1"/>
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>56</v>
@@ -1673,7 +1697,7 @@
         <v>40</v>
       </c>
       <c r="D18" s="11">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E18" s="11">
         <v>130</v>
@@ -1689,11 +1713,11 @@
       </c>
       <c r="I18" s="12">
         <f t="shared" si="2"/>
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="1"/>
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>59</v>
@@ -1719,7 +1743,7 @@
         <v>40</v>
       </c>
       <c r="D19" s="11">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E19" s="11">
         <v>105</v>
@@ -1735,11 +1759,11 @@
       </c>
       <c r="I19" s="12">
         <f t="shared" si="2"/>
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="J19" s="12">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>49</v>
@@ -1765,7 +1789,7 @@
         <v>40</v>
       </c>
       <c r="D20" s="11">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E20" s="11">
         <v>105</v>
@@ -1781,14 +1805,14 @@
       </c>
       <c r="I20" s="12">
         <f t="shared" si="2"/>
-        <v>1205</v>
+        <v>1215</v>
       </c>
       <c r="J20" s="12">
         <f t="shared" si="1"/>
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>50</v>
@@ -1811,10 +1835,10 @@
         <v>40</v>
       </c>
       <c r="D21" s="11">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E21" s="11">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F21" s="11">
         <v>350</v>
@@ -1827,11 +1851,11 @@
       </c>
       <c r="I21" s="12">
         <f t="shared" si="2"/>
-        <v>1152</v>
+        <v>1172</v>
       </c>
       <c r="J21" s="12">
         <f t="shared" si="1"/>
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="K21" s="13" t="s">
         <v>49</v>
@@ -1857,10 +1881,10 @@
         <v>40</v>
       </c>
       <c r="D22" s="11">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E22" s="11">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="F22" s="11">
         <v>200</v>
@@ -1873,14 +1897,14 @@
       </c>
       <c r="I22" s="12">
         <f t="shared" si="2"/>
-        <v>987</v>
+        <v>1062</v>
       </c>
       <c r="J22" s="12">
-        <f t="shared" si="1"/>
-        <v>453</v>
+        <f>IF(I22="","",1440-I22)</f>
+        <v>378</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>62</v>
@@ -1892,150 +1916,286 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46269</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="11">
+        <v>400</v>
+      </c>
+      <c r="C23" s="11">
+        <v>40</v>
+      </c>
+      <c r="D23" s="11">
+        <v>220</v>
+      </c>
+      <c r="E23" s="11">
+        <v>150</v>
+      </c>
+      <c r="F23" s="11">
+        <v>250</v>
+      </c>
+      <c r="G23" s="11">
+        <v>5</v>
+      </c>
+      <c r="H23" s="11">
+        <v>52</v>
+      </c>
+      <c r="I23" s="12">
+        <f t="shared" si="2"/>
+        <v>1112</v>
+      </c>
+      <c r="J23" s="12">
+        <f t="shared" ref="J23:J28" si="3">IF(I23="","",1440-I23)</f>
+        <v>328</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46270</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="11">
+        <v>450</v>
+      </c>
+      <c r="C24" s="11">
+        <v>40</v>
+      </c>
+      <c r="D24" s="11">
+        <v>200</v>
+      </c>
+      <c r="E24" s="11">
+        <v>120</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11">
+        <v>52</v>
+      </c>
+      <c r="I24" s="12">
+        <f t="shared" si="2"/>
+        <v>862</v>
+      </c>
+      <c r="J24" s="12">
+        <f t="shared" si="3"/>
+        <v>578</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>46271</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="11">
+        <v>430</v>
+      </c>
+      <c r="C25" s="11">
+        <v>40</v>
+      </c>
+      <c r="D25" s="11">
+        <v>225</v>
+      </c>
+      <c r="E25" s="11">
+        <v>130</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11">
+        <v>52</v>
+      </c>
+      <c r="I25" s="12">
+        <f t="shared" si="2"/>
+        <v>877</v>
+      </c>
+      <c r="J25" s="12">
+        <f t="shared" si="3"/>
+        <v>563</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46272</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="11">
+        <v>410</v>
+      </c>
+      <c r="C26" s="11">
+        <v>40</v>
+      </c>
+      <c r="D26" s="11">
+        <v>230</v>
+      </c>
+      <c r="E26" s="11">
+        <v>105</v>
+      </c>
+      <c r="F26" s="11">
+        <v>200</v>
+      </c>
+      <c r="G26" s="11">
+        <v>4</v>
+      </c>
+      <c r="H26" s="11">
+        <v>52</v>
+      </c>
+      <c r="I26" s="12">
+        <f t="shared" si="2"/>
+        <v>1037</v>
+      </c>
+      <c r="J26" s="12">
+        <f t="shared" si="3"/>
+        <v>403</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46273</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+      <c r="B27" s="11">
+        <v>300</v>
+      </c>
+      <c r="C27" s="11">
+        <v>40</v>
+      </c>
+      <c r="D27" s="11">
+        <v>210</v>
+      </c>
+      <c r="E27" s="11">
+        <v>140</v>
+      </c>
+      <c r="F27" s="11">
+        <v>350</v>
+      </c>
+      <c r="G27" s="11">
+        <v>7</v>
+      </c>
+      <c r="H27" s="11">
+        <v>52</v>
+      </c>
+      <c r="I27" s="12">
+        <f t="shared" si="2"/>
+        <v>1092</v>
+      </c>
+      <c r="J27" s="12">
+        <f t="shared" si="3"/>
+        <v>348</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="11">
+        <v>420</v>
+      </c>
+      <c r="C28" s="11">
+        <v>40</v>
+      </c>
+      <c r="D28" s="11">
+        <v>215</v>
+      </c>
+      <c r="E28" s="11">
+        <v>120</v>
+      </c>
+      <c r="F28" s="11">
+        <v>350</v>
+      </c>
+      <c r="G28" s="11">
+        <v>7</v>
+      </c>
+      <c r="H28" s="11">
+        <v>52</v>
+      </c>
+      <c r="I28" s="12">
+        <f t="shared" si="2"/>
+        <v>1197</v>
+      </c>
+      <c r="J28" s="12">
+        <f t="shared" si="3"/>
+        <v>243</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
+      <c r="A29" s="8">
+        <v>46275</v>
+      </c>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -2057,7 +2217,9 @@
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
+      <c r="A30" s="8">
+        <v>46276</v>
+      </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -2079,7 +2241,9 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
+      <c r="A31" s="8">
+        <v>46277</v>
+      </c>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
@@ -2101,7 +2265,9 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
+      <c r="A32" s="8">
+        <v>46278</v>
+      </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
@@ -2123,7 +2289,9 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
+      <c r="A33" s="8">
+        <v>46279</v>
+      </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
@@ -2145,7 +2313,9 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
+      <c r="A34" s="8">
+        <v>46280</v>
+      </c>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -2167,7 +2337,9 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
+      <c r="A35" s="8">
+        <v>46281</v>
+      </c>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
@@ -2189,7 +2361,9 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
+      <c r="A36" s="8">
+        <v>46282</v>
+      </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="10"/>
@@ -2211,7 +2385,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
+      <c r="A37" s="8">
+        <v>46283</v>
+      </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -2233,7 +2409,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
+      <c r="A38" s="8">
+        <v>46284</v>
+      </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -2946,11 +3124,11 @@
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="3">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="4">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2968,11 +3146,11 @@
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2990,11 +3168,11 @@
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3012,11 +3190,11 @@
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3034,11 +3212,11 @@
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3056,11 +3234,11 @@
       <c r="G75" s="10"/>
       <c r="H75" s="10"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3078,11 +3256,11 @@
       <c r="G76" s="10"/>
       <c r="H76" s="10"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3100,11 +3278,11 @@
       <c r="G77" s="10"/>
       <c r="H77" s="10"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3122,11 +3300,11 @@
       <c r="G78" s="10"/>
       <c r="H78" s="10"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3144,11 +3322,11 @@
       <c r="G79" s="10"/>
       <c r="H79" s="10"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3166,11 +3344,11 @@
       <c r="G80" s="10"/>
       <c r="H80" s="10"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3188,11 +3366,11 @@
       <c r="G81" s="10"/>
       <c r="H81" s="10"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3210,11 +3388,11 @@
       <c r="G82" s="10"/>
       <c r="H82" s="10"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3232,11 +3410,11 @@
       <c r="G83" s="10"/>
       <c r="H83" s="10"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3254,11 +3432,11 @@
       <c r="G84" s="10"/>
       <c r="H84" s="10"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3276,11 +3454,11 @@
       <c r="G85" s="10"/>
       <c r="H85" s="10"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3298,11 +3476,11 @@
       <c r="G86" s="10"/>
       <c r="H86" s="10"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3320,11 +3498,11 @@
       <c r="G87" s="10"/>
       <c r="H87" s="10"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3342,11 +3520,11 @@
       <c r="G88" s="10"/>
       <c r="H88" s="10"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3364,11 +3542,11 @@
       <c r="G89" s="10"/>
       <c r="H89" s="10"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3386,11 +3564,11 @@
       <c r="G90" s="10"/>
       <c r="H90" s="10"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3408,11 +3586,11 @@
       <c r="G91" s="10"/>
       <c r="H91" s="10"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3430,11 +3608,11 @@
       <c r="G92" s="10"/>
       <c r="H92" s="10"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3452,11 +3630,11 @@
       <c r="G93" s="10"/>
       <c r="H93" s="10"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3474,11 +3652,11 @@
       <c r="G94" s="10"/>
       <c r="H94" s="10"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3496,11 +3674,11 @@
       <c r="G95" s="10"/>
       <c r="H95" s="10"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3518,11 +3696,11 @@
       <c r="G96" s="10"/>
       <c r="H96" s="10"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3540,11 +3718,11 @@
       <c r="G97" s="10"/>
       <c r="H97" s="10"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3562,11 +3740,11 @@
       <c r="G98" s="10"/>
       <c r="H98" s="10"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3584,11 +3762,11 @@
       <c r="G99" s="10"/>
       <c r="H99" s="10"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3606,11 +3784,11 @@
       <c r="G100" s="10"/>
       <c r="H100" s="10"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3628,11 +3806,11 @@
       <c r="G101" s="10"/>
       <c r="H101" s="10"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3650,11 +3828,11 @@
       <c r="G102" s="10"/>
       <c r="H102" s="10"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3672,11 +3850,11 @@
       <c r="G103" s="10"/>
       <c r="H103" s="10"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3694,11 +3872,11 @@
       <c r="G104" s="10"/>
       <c r="H104" s="10"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3716,11 +3894,11 @@
       <c r="G105" s="10"/>
       <c r="H105" s="10"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3738,11 +3916,11 @@
       <c r="G106" s="10"/>
       <c r="H106" s="10"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3760,11 +3938,11 @@
       <c r="G107" s="10"/>
       <c r="H107" s="10"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3782,11 +3960,11 @@
       <c r="G108" s="10"/>
       <c r="H108" s="10"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3804,11 +3982,11 @@
       <c r="G109" s="10"/>
       <c r="H109" s="10"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3826,11 +4004,11 @@
       <c r="G110" s="10"/>
       <c r="H110" s="10"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3848,11 +4026,11 @@
       <c r="G111" s="10"/>
       <c r="H111" s="10"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3870,11 +4048,11 @@
       <c r="G112" s="10"/>
       <c r="H112" s="10"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3892,11 +4070,11 @@
       <c r="G113" s="10"/>
       <c r="H113" s="10"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3914,11 +4092,11 @@
       <c r="G114" s="10"/>
       <c r="H114" s="10"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3936,11 +4114,11 @@
       <c r="G115" s="10"/>
       <c r="H115" s="10"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3958,11 +4136,11 @@
       <c r="G116" s="10"/>
       <c r="H116" s="10"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3980,11 +4158,11 @@
       <c r="G117" s="10"/>
       <c r="H117" s="10"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4002,11 +4180,11 @@
       <c r="G118" s="10"/>
       <c r="H118" s="10"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4024,11 +4202,11 @@
       <c r="G119" s="10"/>
       <c r="H119" s="10"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4046,11 +4224,11 @@
       <c r="G120" s="10"/>
       <c r="H120" s="10"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4068,11 +4246,11 @@
       <c r="G121" s="10"/>
       <c r="H121" s="10"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4090,11 +4268,11 @@
       <c r="G122" s="10"/>
       <c r="H122" s="10"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4112,11 +4290,11 @@
       <c r="G123" s="10"/>
       <c r="H123" s="10"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4134,11 +4312,11 @@
       <c r="G124" s="10"/>
       <c r="H124" s="10"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4156,11 +4334,11 @@
       <c r="G125" s="10"/>
       <c r="H125" s="10"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4178,11 +4356,11 @@
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4200,11 +4378,11 @@
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4222,11 +4400,11 @@
       <c r="G128" s="10"/>
       <c r="H128" s="10"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4244,11 +4422,11 @@
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4266,11 +4444,11 @@
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4288,11 +4466,11 @@
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4310,11 +4488,11 @@
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4332,11 +4510,11 @@
       <c r="G133" s="10"/>
       <c r="H133" s="10"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4354,11 +4532,11 @@
       <c r="G134" s="10"/>
       <c r="H134" s="10"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="5">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="6">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4376,11 +4554,11 @@
       <c r="G135" s="10"/>
       <c r="H135" s="10"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4398,11 +4576,11 @@
       <c r="G136" s="10"/>
       <c r="H136" s="10"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4420,11 +4598,11 @@
       <c r="G137" s="10"/>
       <c r="H137" s="10"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4442,11 +4620,11 @@
       <c r="G138" s="10"/>
       <c r="H138" s="10"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4464,11 +4642,11 @@
       <c r="G139" s="10"/>
       <c r="H139" s="10"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4486,11 +4664,11 @@
       <c r="G140" s="10"/>
       <c r="H140" s="10"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4508,11 +4686,11 @@
       <c r="G141" s="10"/>
       <c r="H141" s="10"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4530,11 +4708,11 @@
       <c r="G142" s="10"/>
       <c r="H142" s="10"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4552,11 +4730,11 @@
       <c r="G143" s="10"/>
       <c r="H143" s="10"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4574,11 +4752,11 @@
       <c r="G144" s="10"/>
       <c r="H144" s="10"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4596,11 +4774,11 @@
       <c r="G145" s="10"/>
       <c r="H145" s="10"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4618,11 +4796,11 @@
       <c r="G146" s="10"/>
       <c r="H146" s="10"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4640,11 +4818,11 @@
       <c r="G147" s="10"/>
       <c r="H147" s="10"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4662,11 +4840,11 @@
       <c r="G148" s="10"/>
       <c r="H148" s="10"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4684,11 +4862,11 @@
       <c r="G149" s="10"/>
       <c r="H149" s="10"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4706,11 +4884,11 @@
       <c r="G150" s="10"/>
       <c r="H150" s="10"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4728,11 +4906,11 @@
       <c r="G151" s="10"/>
       <c r="H151" s="10"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4750,11 +4928,11 @@
       <c r="G152" s="10"/>
       <c r="H152" s="10"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4772,11 +4950,11 @@
       <c r="G153" s="10"/>
       <c r="H153" s="10"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4794,11 +4972,11 @@
       <c r="G154" s="10"/>
       <c r="H154" s="10"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4816,11 +4994,11 @@
       <c r="G155" s="10"/>
       <c r="H155" s="10"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4838,11 +5016,11 @@
       <c r="G156" s="10"/>
       <c r="H156" s="10"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4860,11 +5038,11 @@
       <c r="G157" s="10"/>
       <c r="H157" s="10"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4882,11 +5060,11 @@
       <c r="G158" s="10"/>
       <c r="H158" s="10"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4904,11 +5082,11 @@
       <c r="G159" s="10"/>
       <c r="H159" s="10"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4926,11 +5104,11 @@
       <c r="G160" s="10"/>
       <c r="H160" s="10"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4948,11 +5126,11 @@
       <c r="G161" s="10"/>
       <c r="H161" s="10"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4970,11 +5148,11 @@
       <c r="G162" s="10"/>
       <c r="H162" s="10"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4992,11 +5170,11 @@
       <c r="G163" s="10"/>
       <c r="H163" s="10"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5014,11 +5192,11 @@
       <c r="G164" s="10"/>
       <c r="H164" s="10"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5036,11 +5214,11 @@
       <c r="G165" s="10"/>
       <c r="H165" s="10"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5058,11 +5236,11 @@
       <c r="G166" s="10"/>
       <c r="H166" s="10"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5080,11 +5258,11 @@
       <c r="G167" s="10"/>
       <c r="H167" s="10"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5102,11 +5280,11 @@
       <c r="G168" s="10"/>
       <c r="H168" s="10"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5124,11 +5302,11 @@
       <c r="G169" s="10"/>
       <c r="H169" s="10"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5146,11 +5324,11 @@
       <c r="G170" s="10"/>
       <c r="H170" s="10"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5168,11 +5346,11 @@
       <c r="G171" s="10"/>
       <c r="H171" s="10"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5190,11 +5368,11 @@
       <c r="G172" s="10"/>
       <c r="H172" s="10"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5212,11 +5390,11 @@
       <c r="G173" s="10"/>
       <c r="H173" s="10"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5234,11 +5412,11 @@
       <c r="G174" s="10"/>
       <c r="H174" s="10"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5256,11 +5434,11 @@
       <c r="G175" s="10"/>
       <c r="H175" s="10"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5278,11 +5456,11 @@
       <c r="G176" s="10"/>
       <c r="H176" s="10"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5300,11 +5478,11 @@
       <c r="G177" s="10"/>
       <c r="H177" s="10"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5322,11 +5500,11 @@
       <c r="G178" s="10"/>
       <c r="H178" s="10"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5344,11 +5522,11 @@
       <c r="G179" s="10"/>
       <c r="H179" s="10"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5366,11 +5544,11 @@
       <c r="G180" s="10"/>
       <c r="H180" s="10"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5388,11 +5566,11 @@
       <c r="G181" s="10"/>
       <c r="H181" s="10"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5410,11 +5588,11 @@
       <c r="G182" s="10"/>
       <c r="H182" s="10"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5432,11 +5610,11 @@
       <c r="G183" s="10"/>
       <c r="H183" s="10"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5454,11 +5632,11 @@
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5476,11 +5654,11 @@
       <c r="G185" s="10"/>
       <c r="H185" s="10"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5498,11 +5676,11 @@
       <c r="G186" s="10"/>
       <c r="H186" s="10"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5520,11 +5698,11 @@
       <c r="G187" s="10"/>
       <c r="H187" s="10"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5542,11 +5720,11 @@
       <c r="G188" s="10"/>
       <c r="H188" s="10"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5564,11 +5742,11 @@
       <c r="G189" s="10"/>
       <c r="H189" s="10"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5586,11 +5764,11 @@
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5608,11 +5786,11 @@
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5630,11 +5808,11 @@
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5652,11 +5830,11 @@
       <c r="G193" s="10"/>
       <c r="H193" s="10"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5674,11 +5852,11 @@
       <c r="G194" s="10"/>
       <c r="H194" s="10"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5696,11 +5874,11 @@
       <c r="G195" s="10"/>
       <c r="H195" s="10"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5718,11 +5896,11 @@
       <c r="G196" s="10"/>
       <c r="H196" s="10"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5740,11 +5918,11 @@
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5762,11 +5940,11 @@
       <c r="G198" s="10"/>
       <c r="H198" s="10"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="7">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="8">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5784,11 +5962,11 @@
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5806,11 +5984,11 @@
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5828,11 +6006,11 @@
       <c r="G201" s="10"/>
       <c r="H201" s="10"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5850,11 +6028,11 @@
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5872,11 +6050,11 @@
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5894,11 +6072,11 @@
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5916,11 +6094,11 @@
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5938,11 +6116,11 @@
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5960,11 +6138,11 @@
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5982,11 +6160,11 @@
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6004,11 +6182,11 @@
       <c r="G209" s="10"/>
       <c r="H209" s="10"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6026,11 +6204,11 @@
       <c r="G210" s="10"/>
       <c r="H210" s="10"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6048,11 +6226,11 @@
       <c r="G211" s="10"/>
       <c r="H211" s="10"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6070,11 +6248,11 @@
       <c r="G212" s="10"/>
       <c r="H212" s="10"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6092,11 +6270,11 @@
       <c r="G213" s="10"/>
       <c r="H213" s="10"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6114,11 +6292,11 @@
       <c r="G214" s="10"/>
       <c r="H214" s="10"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6136,11 +6314,11 @@
       <c r="G215" s="10"/>
       <c r="H215" s="10"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6158,11 +6336,11 @@
       <c r="G216" s="10"/>
       <c r="H216" s="10"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6180,11 +6358,11 @@
       <c r="G217" s="10"/>
       <c r="H217" s="10"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6202,11 +6380,11 @@
       <c r="G218" s="10"/>
       <c r="H218" s="10"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6224,11 +6402,11 @@
       <c r="G219" s="10"/>
       <c r="H219" s="10"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6246,11 +6424,11 @@
       <c r="G220" s="10"/>
       <c r="H220" s="10"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6268,11 +6446,11 @@
       <c r="G221" s="10"/>
       <c r="H221" s="10"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6290,11 +6468,11 @@
       <c r="G222" s="10"/>
       <c r="H222" s="10"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6312,11 +6490,11 @@
       <c r="G223" s="10"/>
       <c r="H223" s="10"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6334,11 +6512,11 @@
       <c r="G224" s="10"/>
       <c r="H224" s="10"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6356,11 +6534,11 @@
       <c r="G225" s="10"/>
       <c r="H225" s="10"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6378,11 +6556,11 @@
       <c r="G226" s="10"/>
       <c r="H226" s="10"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6400,11 +6578,11 @@
       <c r="G227" s="10"/>
       <c r="H227" s="10"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6422,11 +6600,11 @@
       <c r="G228" s="10"/>
       <c r="H228" s="10"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6444,11 +6622,11 @@
       <c r="G229" s="10"/>
       <c r="H229" s="10"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6466,11 +6644,11 @@
       <c r="G230" s="10"/>
       <c r="H230" s="10"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6488,11 +6666,11 @@
       <c r="G231" s="10"/>
       <c r="H231" s="10"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6510,11 +6688,11 @@
       <c r="G232" s="10"/>
       <c r="H232" s="10"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6532,11 +6710,11 @@
       <c r="G233" s="10"/>
       <c r="H233" s="10"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6554,11 +6732,11 @@
       <c r="G234" s="10"/>
       <c r="H234" s="10"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6576,11 +6754,11 @@
       <c r="G235" s="10"/>
       <c r="H235" s="10"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6598,11 +6776,11 @@
       <c r="G236" s="10"/>
       <c r="H236" s="10"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6620,11 +6798,11 @@
       <c r="G237" s="10"/>
       <c r="H237" s="10"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6642,11 +6820,11 @@
       <c r="G238" s="10"/>
       <c r="H238" s="10"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6664,11 +6842,11 @@
       <c r="G239" s="10"/>
       <c r="H239" s="10"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6686,11 +6864,11 @@
       <c r="G240" s="10"/>
       <c r="H240" s="10"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6708,11 +6886,11 @@
       <c r="G241" s="10"/>
       <c r="H241" s="10"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6730,11 +6908,11 @@
       <c r="G242" s="10"/>
       <c r="H242" s="10"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6752,11 +6930,11 @@
       <c r="G243" s="10"/>
       <c r="H243" s="10"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6774,11 +6952,11 @@
       <c r="G244" s="10"/>
       <c r="H244" s="10"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6796,11 +6974,11 @@
       <c r="G245" s="10"/>
       <c r="H245" s="10"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6818,11 +6996,11 @@
       <c r="G246" s="10"/>
       <c r="H246" s="10"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6840,11 +7018,11 @@
       <c r="G247" s="10"/>
       <c r="H247" s="10"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6862,11 +7040,11 @@
       <c r="G248" s="10"/>
       <c r="H248" s="10"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6884,11 +7062,11 @@
       <c r="G249" s="10"/>
       <c r="H249" s="10"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6906,11 +7084,11 @@
       <c r="G250" s="10"/>
       <c r="H250" s="10"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6928,11 +7106,11 @@
       <c r="G251" s="10"/>
       <c r="H251" s="10"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6950,11 +7128,11 @@
       <c r="G252" s="10"/>
       <c r="H252" s="10"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6972,11 +7150,11 @@
       <c r="G253" s="10"/>
       <c r="H253" s="10"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6994,11 +7172,11 @@
       <c r="G254" s="10"/>
       <c r="H254" s="10"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7016,11 +7194,11 @@
       <c r="G255" s="10"/>
       <c r="H255" s="10"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7038,11 +7216,11 @@
       <c r="G256" s="10"/>
       <c r="H256" s="10"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7060,11 +7238,11 @@
       <c r="G257" s="10"/>
       <c r="H257" s="10"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7082,11 +7260,11 @@
       <c r="G258" s="10"/>
       <c r="H258" s="10"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7104,11 +7282,11 @@
       <c r="G259" s="10"/>
       <c r="H259" s="10"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7126,11 +7304,11 @@
       <c r="G260" s="10"/>
       <c r="H260" s="10"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7148,11 +7326,11 @@
       <c r="G261" s="10"/>
       <c r="H261" s="10"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7170,11 +7348,11 @@
       <c r="G262" s="10"/>
       <c r="H262" s="10"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="9">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="10">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7192,11 +7370,11 @@
       <c r="G263" s="10"/>
       <c r="H263" s="10"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7214,11 +7392,11 @@
       <c r="G264" s="10"/>
       <c r="H264" s="10"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7236,11 +7414,11 @@
       <c r="G265" s="10"/>
       <c r="H265" s="10"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7258,11 +7436,11 @@
       <c r="G266" s="10"/>
       <c r="H266" s="10"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7280,11 +7458,11 @@
       <c r="G267" s="10"/>
       <c r="H267" s="10"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7302,11 +7480,11 @@
       <c r="G268" s="10"/>
       <c r="H268" s="10"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7324,11 +7502,11 @@
       <c r="G269" s="10"/>
       <c r="H269" s="10"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7346,11 +7524,11 @@
       <c r="G270" s="10"/>
       <c r="H270" s="10"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7368,11 +7546,11 @@
       <c r="G271" s="10"/>
       <c r="H271" s="10"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7390,11 +7568,11 @@
       <c r="G272" s="10"/>
       <c r="H272" s="10"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7412,11 +7590,11 @@
       <c r="G273" s="10"/>
       <c r="H273" s="10"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7434,11 +7612,11 @@
       <c r="G274" s="10"/>
       <c r="H274" s="10"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7456,11 +7634,11 @@
       <c r="G275" s="10"/>
       <c r="H275" s="10"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7478,11 +7656,11 @@
       <c r="G276" s="10"/>
       <c r="H276" s="10"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7500,11 +7678,11 @@
       <c r="G277" s="10"/>
       <c r="H277" s="10"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7522,11 +7700,11 @@
       <c r="G278" s="10"/>
       <c r="H278" s="10"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7544,11 +7722,11 @@
       <c r="G279" s="10"/>
       <c r="H279" s="10"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7566,11 +7744,11 @@
       <c r="G280" s="10"/>
       <c r="H280" s="10"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7588,11 +7766,11 @@
       <c r="G281" s="10"/>
       <c r="H281" s="10"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7610,11 +7788,11 @@
       <c r="G282" s="10"/>
       <c r="H282" s="10"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7632,11 +7810,11 @@
       <c r="G283" s="10"/>
       <c r="H283" s="10"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7654,11 +7832,11 @@
       <c r="G284" s="10"/>
       <c r="H284" s="10"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7676,11 +7854,11 @@
       <c r="G285" s="10"/>
       <c r="H285" s="10"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7698,11 +7876,11 @@
       <c r="G286" s="10"/>
       <c r="H286" s="10"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7720,11 +7898,11 @@
       <c r="G287" s="10"/>
       <c r="H287" s="10"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7742,11 +7920,11 @@
       <c r="G288" s="10"/>
       <c r="H288" s="10"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7764,11 +7942,11 @@
       <c r="G289" s="10"/>
       <c r="H289" s="10"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7786,11 +7964,11 @@
       <c r="G290" s="10"/>
       <c r="H290" s="10"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7808,11 +7986,11 @@
       <c r="G291" s="10"/>
       <c r="H291" s="10"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7830,11 +8008,11 @@
       <c r="G292" s="10"/>
       <c r="H292" s="10"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7852,11 +8030,11 @@
       <c r="G293" s="10"/>
       <c r="H293" s="10"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7874,11 +8052,11 @@
       <c r="G294" s="10"/>
       <c r="H294" s="10"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7896,11 +8074,11 @@
       <c r="G295" s="10"/>
       <c r="H295" s="10"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7918,11 +8096,11 @@
       <c r="G296" s="10"/>
       <c r="H296" s="10"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7940,11 +8118,11 @@
       <c r="G297" s="10"/>
       <c r="H297" s="10"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7962,11 +8140,11 @@
       <c r="G298" s="10"/>
       <c r="H298" s="10"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7984,11 +8162,11 @@
       <c r="G299" s="10"/>
       <c r="H299" s="10"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8006,11 +8184,11 @@
       <c r="G300" s="10"/>
       <c r="H300" s="10"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8028,11 +8206,11 @@
       <c r="G301" s="10"/>
       <c r="H301" s="10"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8050,11 +8228,11 @@
       <c r="G302" s="10"/>
       <c r="H302" s="10"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8072,11 +8250,11 @@
       <c r="G303" s="10"/>
       <c r="H303" s="10"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8094,11 +8272,11 @@
       <c r="G304" s="10"/>
       <c r="H304" s="10"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8116,11 +8294,11 @@
       <c r="G305" s="10"/>
       <c r="H305" s="10"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8138,11 +8316,11 @@
       <c r="G306" s="10"/>
       <c r="H306" s="10"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8160,11 +8338,11 @@
       <c r="G307" s="10"/>
       <c r="H307" s="10"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8182,11 +8360,11 @@
       <c r="G308" s="10"/>
       <c r="H308" s="10"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8204,11 +8382,11 @@
       <c r="G309" s="10"/>
       <c r="H309" s="10"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8226,11 +8404,11 @@
       <c r="G310" s="10"/>
       <c r="H310" s="10"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8248,11 +8426,11 @@
       <c r="G311" s="10"/>
       <c r="H311" s="10"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8270,11 +8448,11 @@
       <c r="G312" s="10"/>
       <c r="H312" s="10"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8292,11 +8470,11 @@
       <c r="G313" s="10"/>
       <c r="H313" s="10"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8314,11 +8492,11 @@
       <c r="G314" s="10"/>
       <c r="H314" s="10"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8336,11 +8514,11 @@
       <c r="G315" s="10"/>
       <c r="H315" s="10"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8358,11 +8536,11 @@
       <c r="G316" s="10"/>
       <c r="H316" s="10"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8380,11 +8558,11 @@
       <c r="G317" s="10"/>
       <c r="H317" s="10"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8402,11 +8580,11 @@
       <c r="G318" s="10"/>
       <c r="H318" s="10"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8424,11 +8602,11 @@
       <c r="G319" s="10"/>
       <c r="H319" s="10"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8446,11 +8624,11 @@
       <c r="G320" s="10"/>
       <c r="H320" s="10"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8468,11 +8646,11 @@
       <c r="G321" s="10"/>
       <c r="H321" s="10"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8490,11 +8668,11 @@
       <c r="G322" s="10"/>
       <c r="H322" s="10"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8512,11 +8690,11 @@
       <c r="G323" s="10"/>
       <c r="H323" s="10"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8534,11 +8712,11 @@
       <c r="G324" s="10"/>
       <c r="H324" s="10"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8556,11 +8734,11 @@
       <c r="G325" s="10"/>
       <c r="H325" s="10"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8578,11 +8756,11 @@
       <c r="G326" s="10"/>
       <c r="H326" s="10"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="11">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="12">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8600,11 +8778,11 @@
       <c r="G327" s="10"/>
       <c r="H327" s="10"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8622,11 +8800,11 @@
       <c r="G328" s="10"/>
       <c r="H328" s="10"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8644,11 +8822,11 @@
       <c r="G329" s="10"/>
       <c r="H329" s="10"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8666,11 +8844,11 @@
       <c r="G330" s="10"/>
       <c r="H330" s="10"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8688,11 +8866,11 @@
       <c r="G331" s="10"/>
       <c r="H331" s="10"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8710,11 +8888,11 @@
       <c r="G332" s="10"/>
       <c r="H332" s="10"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8732,11 +8910,11 @@
       <c r="G333" s="10"/>
       <c r="H333" s="10"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8754,11 +8932,11 @@
       <c r="G334" s="10"/>
       <c r="H334" s="10"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8776,11 +8954,11 @@
       <c r="G335" s="10"/>
       <c r="H335" s="10"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8798,11 +8976,11 @@
       <c r="G336" s="10"/>
       <c r="H336" s="10"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8820,11 +8998,11 @@
       <c r="G337" s="10"/>
       <c r="H337" s="10"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8842,11 +9020,11 @@
       <c r="G338" s="10"/>
       <c r="H338" s="10"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8864,11 +9042,11 @@
       <c r="G339" s="10"/>
       <c r="H339" s="10"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8886,11 +9064,11 @@
       <c r="G340" s="10"/>
       <c r="H340" s="10"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8908,11 +9086,11 @@
       <c r="G341" s="10"/>
       <c r="H341" s="10"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8930,11 +9108,11 @@
       <c r="G342" s="10"/>
       <c r="H342" s="10"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8952,11 +9130,11 @@
       <c r="G343" s="10"/>
       <c r="H343" s="10"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8974,11 +9152,11 @@
       <c r="G344" s="10"/>
       <c r="H344" s="10"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8996,11 +9174,11 @@
       <c r="G345" s="10"/>
       <c r="H345" s="10"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9018,11 +9196,11 @@
       <c r="G346" s="10"/>
       <c r="H346" s="10"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9040,11 +9218,11 @@
       <c r="G347" s="10"/>
       <c r="H347" s="10"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9062,11 +9240,11 @@
       <c r="G348" s="10"/>
       <c r="H348" s="10"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9084,11 +9262,11 @@
       <c r="G349" s="10"/>
       <c r="H349" s="10"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9106,11 +9284,11 @@
       <c r="G350" s="10"/>
       <c r="H350" s="10"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9128,11 +9306,11 @@
       <c r="G351" s="10"/>
       <c r="H351" s="10"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9150,11 +9328,11 @@
       <c r="G352" s="10"/>
       <c r="H352" s="10"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9172,11 +9350,11 @@
       <c r="G353" s="10"/>
       <c r="H353" s="10"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9194,11 +9372,11 @@
       <c r="G354" s="10"/>
       <c r="H354" s="10"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9216,11 +9394,11 @@
       <c r="G355" s="10"/>
       <c r="H355" s="10"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9238,11 +9416,11 @@
       <c r="G356" s="10"/>
       <c r="H356" s="10"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9260,11 +9438,11 @@
       <c r="G357" s="10"/>
       <c r="H357" s="10"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9282,11 +9460,11 @@
       <c r="G358" s="10"/>
       <c r="H358" s="10"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9304,11 +9482,11 @@
       <c r="G359" s="10"/>
       <c r="H359" s="10"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9326,11 +9504,11 @@
       <c r="G360" s="10"/>
       <c r="H360" s="10"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9348,11 +9526,11 @@
       <c r="G361" s="10"/>
       <c r="H361" s="10"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9370,11 +9548,11 @@
       <c r="G362" s="10"/>
       <c r="H362" s="10"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9392,11 +9570,11 @@
       <c r="G363" s="10"/>
       <c r="H363" s="10"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9414,11 +9592,11 @@
       <c r="G364" s="10"/>
       <c r="H364" s="10"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9436,11 +9614,11 @@
       <c r="G365" s="10"/>
       <c r="H365" s="10"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9458,11 +9636,11 @@
       <c r="G366" s="10"/>
       <c r="H366" s="10"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9480,11 +9658,11 @@
       <c r="G367" s="10"/>
       <c r="H367" s="10"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9502,11 +9680,11 @@
       <c r="G368" s="10"/>
       <c r="H368" s="10"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9524,11 +9702,11 @@
       <c r="G369" s="10"/>
       <c r="H369" s="10"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9546,11 +9724,11 @@
       <c r="G370" s="10"/>
       <c r="H370" s="10"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9568,11 +9746,11 @@
       <c r="G371" s="10"/>
       <c r="H371" s="10"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9590,11 +9768,11 @@
       <c r="G372" s="10"/>
       <c r="H372" s="10"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9612,11 +9790,11 @@
       <c r="G373" s="10"/>
       <c r="H373" s="10"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9634,11 +9812,11 @@
       <c r="G374" s="10"/>
       <c r="H374" s="10"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9656,11 +9834,11 @@
       <c r="G375" s="10"/>
       <c r="H375" s="10"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9678,11 +9856,11 @@
       <c r="G376" s="10"/>
       <c r="H376" s="10"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9700,11 +9878,11 @@
       <c r="G377" s="10"/>
       <c r="H377" s="10"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9722,11 +9900,11 @@
       <c r="G378" s="10"/>
       <c r="H378" s="10"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9744,11 +9922,11 @@
       <c r="G379" s="10"/>
       <c r="H379" s="10"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9766,11 +9944,11 @@
       <c r="G380" s="10"/>
       <c r="H380" s="10"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9788,11 +9966,11 @@
       <c r="G381" s="10"/>
       <c r="H381" s="10"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9810,11 +9988,11 @@
       <c r="G382" s="10"/>
       <c r="H382" s="10"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9832,11 +10010,11 @@
       <c r="G383" s="10"/>
       <c r="H383" s="10"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9854,11 +10032,11 @@
       <c r="G384" s="10"/>
       <c r="H384" s="10"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9876,11 +10054,11 @@
       <c r="G385" s="10"/>
       <c r="H385" s="10"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9898,11 +10076,11 @@
       <c r="G386" s="10"/>
       <c r="H386" s="10"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9920,11 +10098,11 @@
       <c r="G387" s="10"/>
       <c r="H387" s="10"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9942,11 +10120,11 @@
       <c r="G388" s="10"/>
       <c r="H388" s="10"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9964,11 +10142,11 @@
       <c r="G389" s="10"/>
       <c r="H389" s="10"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9986,11 +10164,11 @@
       <c r="G390" s="10"/>
       <c r="H390" s="10"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="13">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="14">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10008,11 +10186,11 @@
       <c r="G391" s="10"/>
       <c r="H391" s="10"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10030,11 +10208,11 @@
       <c r="G392" s="10"/>
       <c r="H392" s="10"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10052,11 +10230,11 @@
       <c r="G393" s="10"/>
       <c r="H393" s="10"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10074,11 +10252,11 @@
       <c r="G394" s="10"/>
       <c r="H394" s="10"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10096,11 +10274,11 @@
       <c r="G395" s="10"/>
       <c r="H395" s="10"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10118,11 +10296,11 @@
       <c r="G396" s="10"/>
       <c r="H396" s="10"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10140,11 +10318,11 @@
       <c r="G397" s="10"/>
       <c r="H397" s="10"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10162,11 +10340,11 @@
       <c r="G398" s="10"/>
       <c r="H398" s="10"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10184,11 +10362,11 @@
       <c r="G399" s="10"/>
       <c r="H399" s="10"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10206,11 +10384,11 @@
       <c r="G400" s="10"/>
       <c r="H400" s="10"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10228,11 +10406,11 @@
       <c r="G401" s="10"/>
       <c r="H401" s="10"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12616274.xlsx
+++ b/12616274.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sandeep kumar\Desktop\PYTHON\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23309ED9-CF40-43BA-AF1C-02F149AD732D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45188AF9-1706-4F06-8EE8-CCC316AC055E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,45 @@
   </si>
   <si>
     <t>Enhanced problem-solving and analytical skills.</t>
+  </si>
+  <si>
+    <t>Adapted well to new learning environments and challenges.</t>
+  </si>
+  <si>
+    <t>Demonstrated consistent effort and perseverance in studies.</t>
+  </si>
+  <si>
+    <t>Showed confidence while presenting ideas and opinions.</t>
+  </si>
+  <si>
+    <t>Participated effectively in group discussions and team activities.</t>
+  </si>
+  <si>
+    <t>Consistently completed assigned tasks with dedication.</t>
+  </si>
+  <si>
+    <t>Displayed commitment to achieving educational goals.</t>
+  </si>
+  <si>
+    <t>Engaged actively in practical and project-based learning</t>
+  </si>
+  <si>
+    <t>Completed assignments accurately and on time</t>
+  </si>
+  <si>
+    <t>Demonstrated creativity in problem-solving tasks</t>
+  </si>
+  <si>
+    <t>Showed confidence in expressing ideas and viewpoints</t>
+  </si>
+  <si>
+    <t>Contributed positively to the learning environment.</t>
+  </si>
+  <si>
+    <t>Showed respect for diverse opinions and perspectives</t>
+  </si>
+  <si>
+    <t>Maintained a constructive and solution-oriented attitude</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1429,7 @@
         <v>60</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" ref="I11:I28" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <f t="shared" ref="I11:I42" si="2">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
         <v>740</v>
       </c>
       <c r="J11" s="12">
@@ -1939,15 +1978,15 @@
         <v>5</v>
       </c>
       <c r="H23" s="11">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="I23" s="12">
         <f t="shared" si="2"/>
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" ref="J23:J28" si="3">IF(I23="","",1440-I23)</f>
-        <v>328</v>
+        <f t="shared" ref="J23:J42" si="3">IF(I23="","",1440-I23)</f>
+        <v>300</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>56</v>
@@ -1985,15 +2024,15 @@
         <v>0</v>
       </c>
       <c r="H24" s="11">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="I24" s="12">
         <f t="shared" si="2"/>
-        <v>862</v>
+        <v>885</v>
       </c>
       <c r="J24" s="12">
         <f t="shared" si="3"/>
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>59</v>
@@ -2077,15 +2116,15 @@
         <v>4</v>
       </c>
       <c r="H26" s="11">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I26" s="12">
         <f t="shared" si="2"/>
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="J26" s="12">
         <f t="shared" si="3"/>
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="K26" s="13" t="s">
         <v>56</v>
@@ -2123,15 +2162,15 @@
         <v>7</v>
       </c>
       <c r="H27" s="11">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I27" s="12">
         <f t="shared" si="2"/>
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="J27" s="12">
         <f t="shared" si="3"/>
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="K27" s="13" t="s">
         <v>67</v>
@@ -2169,15 +2208,15 @@
         <v>7</v>
       </c>
       <c r="H28" s="11">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I28" s="12">
         <f t="shared" si="2"/>
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="3"/>
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K28" s="13" t="s">
         <v>78</v>
@@ -2192,333 +2231,649 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>46275</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="11">
+        <v>400</v>
+      </c>
+      <c r="C29" s="11">
+        <v>40</v>
+      </c>
+      <c r="D29" s="11">
+        <v>210</v>
+      </c>
+      <c r="E29" s="11">
+        <v>150</v>
+      </c>
+      <c r="F29" s="11">
+        <v>200</v>
+      </c>
+      <c r="G29" s="11">
+        <v>4</v>
+      </c>
+      <c r="H29" s="11">
+        <v>70</v>
+      </c>
+      <c r="I29" s="12">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J29" s="12">
+        <f t="shared" si="3"/>
+        <v>370</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>46276</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B30" s="11">
+        <v>430</v>
+      </c>
+      <c r="C30" s="11">
+        <v>40</v>
+      </c>
+      <c r="D30" s="11">
+        <v>200</v>
+      </c>
+      <c r="E30" s="11">
+        <v>130</v>
+      </c>
+      <c r="F30" s="11">
+        <v>250</v>
+      </c>
+      <c r="G30" s="11">
+        <v>5</v>
+      </c>
+      <c r="H30" s="11">
+        <v>52</v>
+      </c>
+      <c r="I30" s="12">
+        <f t="shared" si="2"/>
+        <v>1102</v>
+      </c>
+      <c r="J30" s="12">
+        <f t="shared" si="3"/>
+        <v>338</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>46277</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B31" s="11">
+        <v>350</v>
+      </c>
+      <c r="C31" s="11">
+        <v>40</v>
+      </c>
+      <c r="D31" s="11">
+        <v>190</v>
+      </c>
+      <c r="E31" s="11">
+        <v>125</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>55</v>
+      </c>
+      <c r="I31" s="12">
+        <f t="shared" si="2"/>
+        <v>760</v>
+      </c>
+      <c r="J31" s="12">
+        <f t="shared" si="3"/>
+        <v>680</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M31" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>46278</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B32" s="11">
+        <v>370</v>
+      </c>
+      <c r="C32" s="11">
+        <v>40</v>
+      </c>
+      <c r="D32" s="11">
+        <v>250</v>
+      </c>
+      <c r="E32" s="11">
+        <v>120</v>
+      </c>
+      <c r="F32" s="11">
+        <v>0</v>
+      </c>
+      <c r="G32" s="11">
+        <v>0</v>
+      </c>
+      <c r="H32" s="11">
+        <v>59</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="2"/>
+        <v>839</v>
+      </c>
+      <c r="J32" s="12">
+        <f t="shared" si="3"/>
+        <v>601</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46279</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B33" s="11">
+        <v>370</v>
+      </c>
+      <c r="C33" s="11">
+        <v>40</v>
+      </c>
+      <c r="D33" s="11">
+        <v>200</v>
+      </c>
+      <c r="E33" s="11">
+        <v>120</v>
+      </c>
+      <c r="F33" s="11">
+        <v>200</v>
+      </c>
+      <c r="G33" s="11">
+        <v>4</v>
+      </c>
+      <c r="H33" s="11">
+        <v>65</v>
+      </c>
+      <c r="I33" s="12">
+        <f t="shared" si="2"/>
+        <v>995</v>
+      </c>
+      <c r="J33" s="12">
+        <f t="shared" si="3"/>
+        <v>445</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>46280</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B34" s="11">
+        <v>330</v>
+      </c>
+      <c r="C34" s="11">
+        <v>40</v>
+      </c>
+      <c r="D34" s="11">
+        <v>220</v>
+      </c>
+      <c r="E34" s="11">
+        <v>120</v>
+      </c>
+      <c r="F34" s="11">
+        <v>350</v>
+      </c>
+      <c r="G34" s="11">
+        <v>7</v>
+      </c>
+      <c r="H34" s="11">
+        <v>60</v>
+      </c>
+      <c r="I34" s="12">
+        <f t="shared" si="2"/>
+        <v>1120</v>
+      </c>
+      <c r="J34" s="12">
+        <f t="shared" si="3"/>
+        <v>320</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>46281</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B35" s="11">
+        <v>350</v>
+      </c>
+      <c r="C35" s="11">
+        <v>40</v>
+      </c>
+      <c r="D35" s="11">
+        <v>250</v>
+      </c>
+      <c r="E35" s="11">
+        <v>120</v>
+      </c>
+      <c r="F35" s="11">
+        <v>350</v>
+      </c>
+      <c r="G35" s="11">
+        <v>7</v>
+      </c>
+      <c r="H35" s="11">
+        <v>54</v>
+      </c>
+      <c r="I35" s="12">
+        <f t="shared" si="2"/>
+        <v>1164</v>
+      </c>
+      <c r="J35" s="12">
+        <f t="shared" si="3"/>
+        <v>276</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>46282</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B36" s="11">
+        <v>370</v>
+      </c>
+      <c r="C36" s="11">
+        <v>40</v>
+      </c>
+      <c r="D36" s="11">
+        <v>225</v>
+      </c>
+      <c r="E36" s="11">
+        <v>120</v>
+      </c>
+      <c r="F36" s="11">
+        <v>200</v>
+      </c>
+      <c r="G36" s="11">
+        <v>4</v>
+      </c>
+      <c r="H36" s="11">
+        <v>59</v>
+      </c>
+      <c r="I36" s="12">
+        <f t="shared" si="2"/>
+        <v>1014</v>
+      </c>
+      <c r="J36" s="12">
+        <f t="shared" si="3"/>
+        <v>426</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>46283</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B37" s="11">
+        <v>380</v>
+      </c>
+      <c r="C37" s="11">
+        <v>40</v>
+      </c>
+      <c r="D37" s="11">
+        <v>230</v>
+      </c>
+      <c r="E37" s="11">
+        <v>120</v>
+      </c>
+      <c r="F37" s="11">
+        <v>250</v>
+      </c>
+      <c r="G37" s="11">
+        <v>5</v>
+      </c>
+      <c r="H37" s="11">
+        <v>58</v>
+      </c>
+      <c r="I37" s="12">
+        <f t="shared" si="2"/>
+        <v>1078</v>
+      </c>
+      <c r="J37" s="12">
+        <f t="shared" si="3"/>
+        <v>362</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46284</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+      <c r="B38" s="11">
+        <v>370</v>
+      </c>
+      <c r="C38" s="11">
+        <v>40</v>
+      </c>
+      <c r="D38" s="11">
+        <v>240</v>
+      </c>
+      <c r="E38" s="11">
+        <v>120</v>
+      </c>
+      <c r="F38" s="11">
+        <v>0</v>
+      </c>
+      <c r="G38" s="11">
+        <v>0</v>
+      </c>
+      <c r="H38" s="11">
+        <v>50</v>
+      </c>
+      <c r="I38" s="12">
+        <f t="shared" si="2"/>
+        <v>820</v>
+      </c>
+      <c r="J38" s="12">
+        <f t="shared" si="3"/>
+        <v>620</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="11">
+        <v>320</v>
+      </c>
+      <c r="C39" s="11">
+        <v>40</v>
+      </c>
+      <c r="D39" s="11">
+        <v>210</v>
+      </c>
+      <c r="E39" s="11">
+        <v>120</v>
+      </c>
+      <c r="F39" s="11">
+        <v>0</v>
+      </c>
+      <c r="G39" s="11">
+        <v>0</v>
+      </c>
+      <c r="H39" s="11">
+        <v>55</v>
+      </c>
+      <c r="I39" s="12">
+        <f t="shared" si="2"/>
+        <v>745</v>
+      </c>
+      <c r="J39" s="12">
+        <f t="shared" si="3"/>
+        <v>695</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="11">
+        <v>340</v>
+      </c>
+      <c r="C40" s="11">
+        <v>40</v>
+      </c>
+      <c r="D40" s="11">
+        <v>215</v>
+      </c>
+      <c r="E40" s="11">
+        <v>120</v>
+      </c>
+      <c r="F40" s="11">
+        <v>200</v>
+      </c>
+      <c r="G40" s="11">
+        <v>4</v>
+      </c>
+      <c r="H40" s="11">
+        <v>75</v>
+      </c>
+      <c r="I40" s="12">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J40" s="12">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N40" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B41" s="11">
+        <v>370</v>
+      </c>
+      <c r="C41" s="11">
+        <v>40</v>
+      </c>
+      <c r="D41" s="11">
+        <v>214</v>
+      </c>
+      <c r="E41" s="11">
+        <v>120</v>
+      </c>
+      <c r="F41" s="11">
+        <v>350</v>
+      </c>
+      <c r="G41" s="11">
+        <v>7</v>
+      </c>
+      <c r="H41" s="11">
+        <v>68</v>
+      </c>
+      <c r="I41" s="12">
+        <f t="shared" si="2"/>
+        <v>1162</v>
+      </c>
+      <c r="J41" s="12">
+        <f t="shared" si="3"/>
+        <v>278</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B42" s="11">
+        <v>345</v>
+      </c>
+      <c r="C42" s="11">
+        <v>40</v>
+      </c>
+      <c r="D42" s="11">
+        <v>210</v>
+      </c>
+      <c r="E42" s="11">
+        <v>120</v>
+      </c>
+      <c r="F42" s="11">
+        <v>350</v>
+      </c>
+      <c r="G42" s="11">
+        <v>7</v>
+      </c>
+      <c r="H42" s="11">
+        <v>70</v>
+      </c>
+      <c r="I42" s="12">
+        <f t="shared" si="2"/>
+        <v>1135</v>
+      </c>
+      <c r="J42" s="12">
+        <f t="shared" si="3"/>
+        <v>305</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N42" s="14" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
